--- a/UNI/MATES/Modelos/simulacion.xlsx
+++ b/UNI/MATES/Modelos/simulacion.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DOCUMENTOS\INFOMATES\UNI\MATES\Modelos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76F01BA7-A392-4A8C-A2B5-3E11E3F81B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E24233A-37EF-4371-9089-699546D3DF79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ESTABLE" sheetId="1" r:id="rId1"/>
     <sheet name="INESTABLE" sheetId="2" r:id="rId2"/>
     <sheet name="x=0" sheetId="3" r:id="rId3"/>
     <sheet name="x=1" sheetId="4" r:id="rId4"/>
+    <sheet name="2-ciclo" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="52">
   <si>
     <t>a =</t>
   </si>
@@ -238,81 +239,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="28">
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color theme="6" tint="0.39997558519241921"/>
-        </right>
-        <top style="thin">
-          <color theme="6" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="6" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color theme="6" tint="0.39997558519241921"/>
-        </right>
-        <top style="thin">
-          <color theme="6" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="6" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -343,68 +293,18 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color theme="6" tint="0.39997558519241921"/>
-        </right>
-        <top style="thin">
-          <color theme="6" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="6" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color theme="6" tint="0.39997558519241921"/>
-        </right>
-        <top style="thin">
-          <color theme="6" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="6" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -568,6 +468,134 @@
         <horizontal/>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="6" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="6" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="6" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="6" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="6" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="6" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="6" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="6" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="6" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="6" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="6" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="6" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -612,7 +640,7 @@
   <autoFilter ref="A1:B47" xr:uid="{B9EF4A01-9C2E-4694-9F04-709E80E062B0}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{788C80D7-A7E9-4621-AAA3-6C0EC361B179}" name="ITERACIÓN-iesima"/>
-    <tableColumn id="2" xr3:uid="{FEE69873-D6BE-4162-B037-AD1E123B250E}" name="VALOR" dataDxfId="23">
+    <tableColumn id="2" xr3:uid="{FEE69873-D6BE-4162-B037-AD1E123B250E}" name="VALOR" dataDxfId="27">
       <calculatedColumnFormula>B1 + $S$3*B1*(B1-$S$4)*(1-B1)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -625,7 +653,7 @@
   <autoFilter ref="D1:E47" xr:uid="{4DC42446-A667-4099-A46B-E88BF3FDE1E2}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{2FABA3DD-738A-42CE-AB99-79256A281368}" name="ITERACIÓN-iesima"/>
-    <tableColumn id="2" xr3:uid="{3D0841EA-8F40-4E29-801B-D7D9168632BD}" name="VALOR" dataDxfId="22">
+    <tableColumn id="2" xr3:uid="{3D0841EA-8F40-4E29-801B-D7D9168632BD}" name="VALOR" dataDxfId="26">
       <calculatedColumnFormula>E1 + $S$3*E1*(E1-$S$4)*(1-E1)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -638,7 +666,7 @@
   <autoFilter ref="A1:B47" xr:uid="{56E4D0EC-BFFE-4F63-BDCD-8282A561155E}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{F9C84279-1C88-4E5E-AE84-B58D7AD2C50B}" name="ITERACIÓN-iesima"/>
-    <tableColumn id="2" xr3:uid="{9A677163-F7E2-458D-B864-19C873B0FB91}" name="VALOR" dataDxfId="7">
+    <tableColumn id="2" xr3:uid="{9A677163-F7E2-458D-B864-19C873B0FB91}" name="VALOR" dataDxfId="25">
       <calculatedColumnFormula>B1 + $S$3*B1*(B1-$S$4)*(1-B1)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -651,7 +679,7 @@
   <autoFilter ref="D1:E47" xr:uid="{9AC8EE9D-6798-4EFB-8FFA-404B0E897066}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{15D5A429-12F4-48AD-BD0F-65F54B2E2DF6}" name="ITERACIÓN-iesima"/>
-    <tableColumn id="2" xr3:uid="{29AE2148-6A7B-450E-AA9A-3B9C337DDC85}" name="VALOR" dataDxfId="6">
+    <tableColumn id="2" xr3:uid="{29AE2148-6A7B-450E-AA9A-3B9C337DDC85}" name="VALOR" dataDxfId="24">
       <calculatedColumnFormula>E1 + $S$3*E1*(E1-$S$4)*(1-E1)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -664,7 +692,7 @@
   <autoFilter ref="A1:B47" xr:uid="{6769061B-18D6-40FC-B6C1-6CA9AED435A9}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{B0CAFA4B-2ACF-4B80-8F44-74CFC6E495F9}" name="ITERACIÓN-iesima"/>
-    <tableColumn id="2" xr3:uid="{1B14F349-1332-4A39-8952-5B9005472353}" name="VALOR" dataDxfId="1">
+    <tableColumn id="2" xr3:uid="{1B14F349-1332-4A39-8952-5B9005472353}" name="VALOR" dataDxfId="23">
       <calculatedColumnFormula>B1 + $S$3*B1*(B1-$S$4)*(1-B1)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -677,7 +705,7 @@
   <autoFilter ref="D1:E47" xr:uid="{F9E8BB7B-4A44-45E5-A4FE-5C22C7BCFE40}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{8E6E3AEF-5997-473E-BDAF-2AF7F0645C51}" name="ITERACIÓN-iesima"/>
-    <tableColumn id="2" xr3:uid="{843634B7-03D6-4824-BD68-35C326EF17EB}" name="VALOR" dataDxfId="0">
+    <tableColumn id="2" xr3:uid="{843634B7-03D6-4824-BD68-35C326EF17EB}" name="VALOR" dataDxfId="22">
       <calculatedColumnFormula>E1 + $S$3*E1*(E1-$S$4)*(1-E1)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -959,8 +987,7 @@
     <col min="6" max="6" width="11.42578125" customWidth="1"/>
     <col min="7" max="7" width="9.140625" customWidth="1"/>
     <col min="8" max="8" width="13.85546875" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" style="3" customWidth="1"/>
-    <col min="10" max="12" width="11.42578125" customWidth="1"/>
+    <col min="9" max="12" width="11.42578125" customWidth="1"/>
     <col min="15" max="15" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1760,14 +1787,14 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N6">
-    <cfRule type="containsText" dxfId="19" priority="4" operator="containsText" text="FALSO">
-      <formula>NOT(ISERROR(SEARCH("FALSO",N6)))</formula>
+  <conditionalFormatting sqref="H8">
+    <cfRule type="containsText" dxfId="19" priority="1" operator="containsText" text="FALSO">
+      <formula>NOT(ISERROR(SEARCH("FALSO",H8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="5" operator="containsText" text="VERDADERO">
-      <formula>NOT(ISERROR(SEARCH("VERDADERO",N6)))</formula>
+    <cfRule type="containsText" dxfId="18" priority="2" operator="containsText" text="VERDADERO">
+      <formula>NOT(ISERROR(SEARCH("VERDADERO",H8)))</formula>
     </cfRule>
-    <cfRule type="colorScale" priority="6">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -1778,14 +1805,14 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H8">
-    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="FALSO">
-      <formula>NOT(ISERROR(SEARCH("FALSO",H8)))</formula>
+  <conditionalFormatting sqref="N6">
+    <cfRule type="containsText" dxfId="17" priority="4" operator="containsText" text="FALSO">
+      <formula>NOT(ISERROR(SEARCH("FALSO",N6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="2" operator="containsText" text="VERDADERO">
-      <formula>NOT(ISERROR(SEARCH("VERDADERO",H8)))</formula>
+    <cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="VERDADERO">
+      <formula>NOT(ISERROR(SEARCH("VERDADERO",N6)))</formula>
     </cfRule>
-    <cfRule type="colorScale" priority="3">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2593,10 +2620,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H6">
-    <cfRule type="containsText" dxfId="17" priority="4" operator="containsText" text="FALSO">
+    <cfRule type="containsText" dxfId="15" priority="4" operator="containsText" text="FALSO">
       <formula>NOT(ISERROR(SEARCH("FALSO",H6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="VERDADERO">
+    <cfRule type="containsText" dxfId="14" priority="5" operator="containsText" text="VERDADERO">
       <formula>NOT(ISERROR(SEARCH("VERDADERO",H6)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -4260,10 +4287,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H6">
-    <cfRule type="containsText" dxfId="5" priority="4" operator="containsText" text="FALSO">
+    <cfRule type="containsText" dxfId="7" priority="4" operator="containsText" text="FALSO">
       <formula>NOT(ISERROR(SEARCH("FALSO",H6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="VERDADERO">
+    <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="VERDADERO">
       <formula>NOT(ISERROR(SEARCH("VERDADERO",H6)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -4278,10 +4305,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="FALSO">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="FALSO">
       <formula>NOT(ISERROR(SEARCH("FALSO",H8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="VERDADERO">
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="VERDADERO">
       <formula>NOT(ISERROR(SEARCH("VERDADERO",H8)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="3">
@@ -4297,11 +4324,554 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="B3:B47 E2:E47" calculatedColumn="1"/>
+    <ignoredError sqref="B4:B47 E2:E47" calculatedColumn="1"/>
   </ignoredErrors>
   <tableParts count="2">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED6C445C-ACCE-42E0-ADE5-E0AB7F1B5BBD}">
+  <dimension ref="A1:H47"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.28515625" customWidth="1"/>
+    <col min="2" max="2" width="26.7109375" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="8" max="8" width="13.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <f>B2 + $H$3*B2*(B2-$H$4)*(1-B2)</f>
+        <v>0.70079999999999998</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="G3" t="s">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2">
+        <f t="shared" ref="B4:B47" si="0">B3 + $H$3*B3*(B3-$H$4)*(1-B3)</f>
+        <v>0.87763518504960003</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="G4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2">
+        <f>B4 + $H$3*B4*(B4-$H$4)*(1-B4)</f>
+        <v>1.0479656476388981</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2">
+        <f t="shared" si="0"/>
+        <v>0.93227986661991158</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="G6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2">
+        <f t="shared" si="0"/>
+        <v>1.046904618704606</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2">
+        <f t="shared" si="0"/>
+        <v>0.93411123971503718</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="G8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0463286533287179</v>
+      </c>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2">
+        <f t="shared" si="0"/>
+        <v>0.93509887701009442</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0460028232525804</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="2">
+        <f t="shared" si="0"/>
+        <v>0.93565557153769918</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0458144532722382</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="2">
+        <f t="shared" si="0"/>
+        <v>0.93597674323537916</v>
+      </c>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0457042302871025</v>
+      </c>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="2">
+        <f t="shared" si="0"/>
+        <v>0.93616444758672746</v>
+      </c>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0456392873322138</v>
+      </c>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="2">
+        <f t="shared" si="0"/>
+        <v>0.93627496404107835</v>
+      </c>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0456008691411944</v>
+      </c>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="2">
+        <f t="shared" si="0"/>
+        <v>0.93634031476708468</v>
+      </c>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0455780884732815</v>
+      </c>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="2">
+        <f t="shared" si="0"/>
+        <v>0.93637905591904425</v>
+      </c>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0455645614899902</v>
+      </c>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="2">
+        <f t="shared" si="0"/>
+        <v>0.93640205673732568</v>
+      </c>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0455565226432102</v>
+      </c>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="2">
+        <f t="shared" si="0"/>
+        <v>0.93641572452484934</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0455517429595524</v>
+      </c>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="2">
+        <f t="shared" si="0"/>
+        <v>0.93642385060521882</v>
+      </c>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0455489002607161</v>
+      </c>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="2">
+        <f t="shared" si="0"/>
+        <v>0.93642868341193786</v>
+      </c>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0455472092840192</v>
+      </c>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" s="2">
+        <f t="shared" si="0"/>
+        <v>0.93643155814971657</v>
+      </c>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0455462033047374</v>
+      </c>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="2">
+        <f t="shared" si="0"/>
+        <v>0.93643326834188878</v>
+      </c>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0455456048008109</v>
+      </c>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="2">
+        <f t="shared" si="0"/>
+        <v>0.93643428580826016</v>
+      </c>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0455452487099994</v>
+      </c>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="2">
+        <f t="shared" si="0"/>
+        <v>0.93643489116607226</v>
+      </c>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0455450368427013</v>
+      </c>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="2">
+        <f t="shared" si="0"/>
+        <v>0.93643525134169425</v>
+      </c>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0455449107840431</v>
+      </c>
+      <c r="E41" s="2"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="2">
+        <f t="shared" si="0"/>
+        <v>0.93643546564184332</v>
+      </c>
+      <c r="E42" s="2"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0455448357799855</v>
+      </c>
+      <c r="E43" s="2"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="2">
+        <f t="shared" si="0"/>
+        <v>0.93643559314889357</v>
+      </c>
+      <c r="E44" s="2"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0455447911528699</v>
+      </c>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46" s="2">
+        <f t="shared" si="0"/>
+        <v>0.93643566901504394</v>
+      </c>
+      <c r="E46" s="2"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0455447645998419</v>
+      </c>
+      <c r="E47" s="2"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="H6">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="FALSO">
+      <formula>NOT(ISERROR(SEARCH("FALSO",H6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="VERDADERO">
+      <formula>NOT(ISERROR(SEARCH("VERDADERO",H6)))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H8">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="FALSO">
+      <formula>NOT(ISERROR(SEARCH("FALSO",H8)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="VERDADERO">
+      <formula>NOT(ISERROR(SEARCH("VERDADERO",H8)))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>